--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -8,13 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86A号 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86B号 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86C号 销控表" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86D号 销控表" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86E号 销控表" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86F号 销控表" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="薄扶林道86G号 销控表" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="独立屋销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,7 +600,7 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
@@ -702,7 +696,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -798,7 +792,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -844,7 +838,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -890,7 +884,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1020,17 +1014,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Mount Pokfulam - 薄扶林道86A号 销控网格图</t>
+          <t>Mount Pokfulam - 独立屋销控网格图</t>
         </is>
       </c>
     </row>
@@ -1069,785 +1069,150 @@
     <row r="3" ht="25" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
+          <t>7 套</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
           <t>1 套</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="C3" s="13" t="inlineStr">
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>4 套</t>
+        </is>
+      </c>
+      <c r="E3" s="15" t="inlineStr">
         <is>
           <t>0 套</t>
         </is>
       </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
       <c r="F3" s="11" t="inlineStr">
         <is>
-          <t>0 套</t>
+          <t>2 套</t>
         </is>
       </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>楼层\房号</t>
+          <t>类型/位置</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
+          <t>薄扶林道86A号</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86B号</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86C号</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86D号</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86E号</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86F号</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>薄扶林道86G号</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="80" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>-/F</t>
+          <t>独立屋</t>
         </is>
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>- | 3643呎 (4+房)
-$15,939万
-$43,752/呎
-(已售)</t>
+          <t>薄扶林道86A号
+3643呎 (4+房)
+(25年-09月)
+$1.59亿
+$43,752/呎</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>薄扶林道86B号
+4810呎 (4+房)
+(在售)
+招标项目
+-</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>薄扶林道86C号
+4683呎 (3房)
+(25年-04月)
+$2.30亿
+$49,220/呎</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="inlineStr">
+        <is>
+          <t>薄扶林道86D号
+4765呎 (4+房)
+(24年-05月)
+$3.34亿
+$70,000/呎</t>
+        </is>
+      </c>
+      <c r="F6" s="16" t="inlineStr">
+        <is>
+          <t>薄扶林道86E号
+4578呎 (4+房)
+(25年-08月)
+$1.89亿
+$41,337/呎</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
+        <is>
+          <t>薄扶林道86F号
+4717呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>薄扶林道86G号
+3654呎 (4+房)
+(待售)
+暂无价格
+暂无呎价</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86B号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>- | 4810呎 (4+房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86C号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 4683呎 (3房)
-$23,050万
-$49,220/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86D号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 4765呎 (4+房)
-$33,355万
-$70,000/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86E号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>- | 4578呎 (4+房)
-$18,924万
-$41,337/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86F号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>- | 4717呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Mount Pokfulam - 薄扶林道86G号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>1 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>-/F</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>- | 3654呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,6 +98,22 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="8">
@@ -217,13 +233,13 @@
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -601,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -617,7 +617,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -607,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -620,6 +620,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -677,6 +681,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -723,6 +747,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -773,6 +817,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>招标单位</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>是</t>
         </is>
       </c>
@@ -819,6 +883,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -865,6 +949,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -911,6 +1015,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -961,6 +1085,26 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1011,13 +1155,33 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1166,7 +1330,7 @@
         <is>
           <t>薄扶林道86A号
 3643呎 (4+房)
-(25年-09月)
+(25年-09月-17日)
 $1.59亿
 $43,752/呎</t>
         </is>
@@ -1184,7 +1348,7 @@
         <is>
           <t>薄扶林道86C号
 4683呎 (3房)
-(25年-04月)
+(25年-04月-29日)
 $2.30亿
 $49,220/呎</t>
         </is>
@@ -1193,7 +1357,7 @@
         <is>
           <t>薄扶林道86D号
 4765呎 (4+房)
-(24年-05月)
+(24年-05月-09日)
 $3.34亿
 $70,000/呎</t>
         </is>
@@ -1202,7 +1366,7 @@
         <is>
           <t>薄扶林道86E号
 4578呎 (4+房)
-(25年-08月)
+(25年-08月-26日)
 $1.89亿
 $41,337/呎</t>
         </is>

--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -1330,7 +1330,7 @@
         <is>
           <t>薄扶林道86A号
 3643呎 (4+房)
-(25年-09月-17日)
+(25年-09月)
 $1.59亿
 $43,752/呎</t>
         </is>
@@ -1348,7 +1348,7 @@
         <is>
           <t>薄扶林道86C号
 4683呎 (3房)
-(25年-04月-29日)
+(25年-04月)
 $2.30亿
 $49,220/呎</t>
         </is>
@@ -1357,7 +1357,7 @@
         <is>
           <t>薄扶林道86D号
 4765呎 (4+房)
-(24年-05月-09日)
+(24年-05月)
 $3.34亿
 $70,000/呎</t>
         </is>
@@ -1366,7 +1366,7 @@
         <is>
           <t>薄扶林道86E号
 4578呎 (4+房)
-(25年-08月-26日)
+(25年-08月)
 $1.89亿
 $41,337/呎</t>
         </is>

--- a/files/港岛-半山区西部-Mount Pokfulam.xlsx
+++ b/files/港岛-半山区西部-Mount Pokfulam.xlsx
@@ -1330,7 +1330,7 @@
         <is>
           <t>薄扶林道86A号
 3643呎 (4+房)
-(25年-09月)
+(25年-09月-17日)
 $1.59亿
 $43,752/呎</t>
         </is>
@@ -1348,7 +1348,7 @@
         <is>
           <t>薄扶林道86C号
 4683呎 (3房)
-(25年-04月)
+(25年-04月-29日)
 $2.30亿
 $49,220/呎</t>
         </is>
@@ -1357,7 +1357,7 @@
         <is>
           <t>薄扶林道86D号
 4765呎 (4+房)
-(24年-05月)
+(24年-05月-09日)
 $3.34亿
 $70,000/呎</t>
         </is>
@@ -1366,7 +1366,7 @@
         <is>
           <t>薄扶林道86E号
 4578呎 (4+房)
-(25年-08月)
+(25年-08月-26日)
 $1.89亿
 $41,337/呎</t>
         </is>
